--- a/매개체감염병_지식베이스_카카오형식.xlsx
+++ b/매개체감염병_지식베이스_카카오형식.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ_업데이트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FAQ_통합본" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -530,24 +530,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>예방수칙</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>반려동물</t>
-        </is>
-      </c>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>반려동물과 산책 시 진드기 감염(SFTS)을 예방하려면 어떻게 하나요?</t>
+          <t>매개체감염병이란 무엇인가요?</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>반려동물 산책 시 진드기 방지 옷을 입히거나 기피제를 사용하고 가급적 풀숲을 피하는 것이 좋아요. 외출 후에는 귀 안쪽, 발가락 사이, 가슴 아랫부분 등 진드기가 잘 붙는 부위를 꼼꼼히 확인해 주세요. 진드기를 발견했다면 맨손으로 만지지 말고 핀셋 등 제거 도구를 사용해 피부에 가깝게 잡아 떼어내야 하며, 제거 후 동물병원 진료를 권장해요.</t>
+          <t>매개체감염병이란 모기·진드기·벼룩 등 살아있는 곤충(매개체)이 바이러스, 세균, 기생충 등 병원체를 사람에게 옮겨 발생하는 감염병을 말해요. 우리나라에서는 모기 매개 말라리아·뎅기열, 진드기 매개 SFTS·쯔쯔가무시증·라임병 등이 대표적이에요. 매개체의 활동 시기(주로 봄~가을)에 야외활동 시 각별히 주의하고, 물리지 않도록 예방수칙을 실천하는 것이 중요하답니다.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -564,76 +560,68 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>신고·진료·위험지역</t>
+          <t>매개체감염병 기본정보</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>말라리아</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>헌혈</t>
-        </is>
-      </c>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>말라리아 위험지역을 방문했는데 헌혈이 가능한가요?</t>
+          <t>우리나라에서 주로 발생하는 매개체감염병은 무엇인가요?</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>말라리아 국내 헌혈제한지역에 1박 이상 숙박(거주 또는 군복무 포함)한 경우, 1년간 전혈 및 혈소판 성분 헌혈을 할 수 없으며 혈장 성분 헌혈만 가능해요. 말라리아 위험지역에서 벗어난 후 발열 등 의심 증상이 발생하면 즉시 가까운 병원을 찾아 의사에게 방문 이력을 알리고 진료를 받아주세요.</t>
+          <t>국내에서 주로 발생하는 매개체감염병으로는 모기 매개인 말라리아, 진드기 매개인 SFTS(중증열성혈소판감소증후군)·쯔쯔가무시증·라임병이 있어요. 해외여행 후 국내로 유입되는 질병으로는 뎅기열·지카바이러스감염증·웨스트나일열 등이 있습니다. 특히 쯔쯔가무시증은 매년 수천 건 이상 신고되는 가장 흔한 진드기매개감염병이며, SFTS는 치명률이 높아 특별한 주의가 필요해요.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://bloodinfo.net</t>
+          <t>https://www.kdca.go.kr</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>혈액관리본부 확인</t>
+          <t>자세히 보기</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>신고·진료·위험지역</t>
+          <t>매개체감염병 기본정보</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>말라리아</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>진료 및 치료</t>
-        </is>
-      </c>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>말라리아 약을 먹고 토했는데 다시 먹어야 하나요?</t>
+          <t>매개체감염병은 사람 간 전파가 되나요?</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>말라리아 약 복용 후 30분 이내에 구토를 했다면 약물이 제대로 흡수되지 않았을 가능성이 있어 다시 복용하는 것을 권장해요. 하지만 복용 후 30분이 지난 이후에 구토했다면 약물이 충분히 흡수된 것으로 보아 다시 드시지 않아도 됩니다. 구토가 심할 경우 의료기관을 방문해 항구토제 처방 등을 상담해 보세요.</t>
+          <t>대부분의 매개체감염병은 모기·진드기 등 매개체를 통해서만 전파되며 사람 간 직접 전파는 일반적으로 일어나지 않아요. 다만 SFTS(중증열성혈소판감소증후군)의 경우, 중증 환자나 사망자의 혈액·체액에 직접 노출될 경우 예외적으로 사람 간 전파가 가능한 것으로 알려져 있어요. 따라서 SFTS 환자를 간호하거나 치료할 때는 장갑·마스크·가운 등 개인보호장구를 반드시 착용해야 합니다.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -650,33 +638,29 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>신고·진료·위험지역</t>
+          <t>매개체감염병 기본정보</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>말라리아</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>진료 및 치료</t>
-        </is>
-      </c>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>말라리아 치료가 끝났는데도 계속 피곤해요. 후유증인가요?</t>
+          <t>기후변화와 매개체감염병은 어떤 관계가 있나요?</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>말라리아 치료 후에도 수일에서 수주 간 피로감이나 무기력증이 계속되는 경우가 있어요. 이는 감염 기간 동안 발생한 염증에 대한 몸의 자연스러운 회복기 반응일 수 있습니다. 보통 시간이 지나면 호전되지만, 증상이 너무 길어지거나 일상생활이 힘들다면 병원을 다시 방문해 진료를 받아보시는 것이 좋습니다.</t>
+          <t>기후변화로 기온이 상승하면 모기와 진드기의 서식 범위가 확대되고 활동 기간이 길어져 매개체감염병 발생 위험이 높아져요. 국내 말라리아 위험지역이 기존 30개 시군구에서 2024년 53개로 확대된 것도 이러한 변화를 반영한 것이랍니다. 열대·아열대 기후에서 유행하던 뎅기열·지카바이러스감염증 등이 국내로 유입될 가능성도 커지고 있어요. 그만큼 야외활동 시 매개체 예방수칙을 평소에 꾸준히 실천하는 것이 중요합니다.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -693,7 +677,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -702,24 +686,20 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>모기매개감염병</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>해외유입</t>
-        </is>
-      </c>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>해외여행 시 모기매개감염병(뎅기열, 지카 등)을 예방하려면?</t>
+          <t>매개체감염병 예방에서 가장 중요한 것은 무엇인가요?</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>여행 전 방문할 국가의 감염병 발생 정보를 미리 확인하세요! 여행 중에는 밝은색 긴팔과 긴바지를 입어 피부 노출을 최소화하고, 모기 기피제를 꼼꼼히 발라주세요. 방충망이나 모기장이 있는 숙소를 이용하는 것도 중요합니다. 귀국 후 2주 이내에 발열, 발진, 두통 등이 나타나면 즉시 1339에 전화하거나 의료기관을 방문해 여행력을 꼭 알려주세요.</t>
+          <t>매개체감염병 예방의 핵심은 모기나 진드기에 물리지 않는 것이에요. 야외활동 시 긴 소매·긴 바지를 착용하고, 피부 노출 부위에 기피제를 뿌려 주세요. 진드기가 많은 풀밭·숲에서는 옷 속으로 진드기가 침입하지 못하도록 소매와 바지단을 여며야 해요. 귀가 후에는 샤워하며 온몸을 꼼꼼히 확인하고, 의심 증상(발열·두통·발진 등)이 나타나면 즉시 의료기관을 방문해 야외활동 이력을 알리는 것이 중요합니다.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -729,40 +709,36 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>해외감염병NOW</t>
+          <t>자세히 보기</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>매개체감염병 기본정보</t>
+          <t>말라리아</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>인수공통감염병</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>개요</t>
-        </is>
-      </c>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>인수공통감염병이 무엇이고 어떻게 예방하나요?</t>
+          <t>말라리아란 무엇인가요?</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>인수공통감염병은 사람과 동물 사이에서 서로 전파되는 병원체에 의해 발생하는 감염병이에요. 예방을 위해서는 야생동물이나 유기동물과의 직접적인 접촉을 피하고, 농작업이나 야외 활동 시 오염된 물이나 토양에 피부가 닿지 않도록 장화, 장갑 등 보호장구를 반드시 착용해야 합니다. 작업 후에는 꼭 깨끗하게 샤워해 주세요.</t>
+          <t>말라리아는 말라리아 원충(Plasmodium)에 감염된 얼룩날개모기류(Anopheles)에 물려 감염되는 기생충 질환이에요. 사람에게 감염되는 말라리아 원충은 삼일열·열대열·사일열·난형열 4종류가 있으며, 국내에서는 삼일열 말라리아가 주로 발생해요. 삼일열 말라리아는 48시간 주기로 발열이 반복되는 것이 특징이며, 완치가 가능한 질병이랍니다. 전 세계적으로는 열대열 말라리아가 치명적인 경우가 많아 해외여행 전 반드시 예방약 복용 여부를 확인해야 해요.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -779,46 +755,3273 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>신고·진료·위험지역</t>
+          <t>말라리아</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>진드기설치류 매개</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>진단 및 관리</t>
-        </is>
-      </c>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
+          <t>말라리아 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>말라리아의 주요 증상은 발열, 오한(심하게 춥고 떨림), 발한, 두통, 근육통, 오심, 구토 등이에요. 국내에서 발생하는 삼일열 말라리아는 48시간(2일) 간격으로 오한→고열→발한 순서로 증상이 반복되는 것이 특징이에요. 초기에는 전신 권태감·피로감만 나타날 수 있어 감기와 혼동되기 쉬워요. 말라리아 위험지역 거주자나 방문자가 37.5℃ 이상 발열이 있으면 반드시 말라리아를 의심하고 보건소나 의료기관에서 신속진단검사(RDT)를 받아보세요.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>국내 말라리아 위험지역은 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>2024년 기준 국내 말라리아 위험지역은 서울(13개), 경기(22개), 인천(10개), 강원(8개) 4개 시·도 내 총 53개 시군구예요. 기존 30개에서 환자 발생 이동 추세를 반영하여 2024년부터 확대되었어요. 특히 휴전선 인접 지역인 파주·철원·강화 등에서 환자 발생이 많으며, 해당 지역에서 야간 야외활동 시 각별한 주의가 필요해요. 위험지역 거주자나 방문자 중 의심 증상이 있으면 가까운 보건소에서 무료 검사를 받을 수 있답니다.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 잠복기는 얼마나 되나요?</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 잠복기는 원충 종류에 따라 다양해요. 국내 삼일열 말라리아는 단기 잠복기(12~18일)와 장기 잠복기(6~12개월) 두 가지 유형이 있어요. 특히 장기 잠복기 유형은 모기에 물린 해가 아닌 이듬해 봄에 발병하는 경우도 있어서, 전년도 위험지역 방문 후 별 이상이 없었더라도 이듬해 발열이 생기면 말라리아 검사를 꼭 받아보세요. 열대열은 7~14일, 사일열은 18~40일, 난형열은 12~18일 정도예요.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 예방약이 있나요?</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>네, 말라리아 예방약이 있어요. 주요 예방약으로는 클로로퀸(주 1회, 출발 1주 전부터 귀국 후 4주간), 독시사이클린(매일 복용, 출발 2일 전~귀국 후 4주간), 아토바쿠온/프로구아닐 복합제(매일 복용, 출발 1~2일 전~귀국 후 7일간), 메플로퀸(주 1회, 출발 1~2주 전~귀국 후 4주간) 등이 있어요. 지역별 약제 내성 양상이 다르므로, 여행 전 반드시 감염내과 전문의나 보건소에서 방문 국가에 맞는 예방약을 처방받으세요.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>말라리아는 어떻게 치료하나요?</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>말라리아는 신속히 치료하면 완치가 가능해요. 국내 삼일열 말라리아는 클로로퀸으로 혈중 원충을 제거한 뒤 간 내 잠복 원충 제거를 위해 프리마퀸을 추가 투여해요. 열대열 말라리아는 클로로퀸 내성이 많아 아르테미시닌 기반 병합요법(ACT) 등을 사용해요. 의심 증상이 있으면 즉시 의료기관을 방문해야 하며, 진단은 신속항원검사(RDT)와 현미경검사·유전자검사(PCR)로 확진합니다. 자가 판단 없이 반드시 의사의 처방을 받으세요.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>해외여행 후 말라리아가 의심될 때 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 유행 국가 여행 후 귀국 시 입국장 검역관에게 증상을 알리고 검역 신고를 해 주세요. 귀국 후 발열·오한·두통 등 의심 증상이 나타나면 즉시 가까운 의료기관에 방문해 해외여행 이력(방문 국가·기간)을 반드시 알려주세요. 열대열 말라리아는 치료가 늦어지면 위험할 수 있으므로 빠른 검사와 치료가 중요해요. 일부 보건소와 국립검역소에서 무료 검사를 받을 수 있으니 질병관리청(1339)에 문의해 보세요.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 예방접종이 있나요?</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>현재 국내에서 일반적으로 사용 가능한 말라리아 백신은 없어요. WHO는 아프리카 소아를 대상으로 RTS,S/AS01(Mosquirix) 백신을 권고하고 있으나, 국내에는 도입되지 않았어요. 따라서 말라리아 예방을 위해서는 예방약 복용(의사 처방 필수)과 모기에 물리지 않는 행동 예방이 핵심이에요. 말라리아 유행 국가를 여행할 계획이라면 출발 4주 전에 여행 클리닉이나 감염내과를 방문해 예방 상담을 받으시길 권해요.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>SFTS란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군, Severe Fever with Thrombocytopenia Syndrome)는 SFTS 바이러스를 보유한 작은소참진드기에 물려 감염되는 인수공통감염병이에요. 주로 4월~11월, 진드기 활동이 활발한 시기에 농작업·등산·야외활동 중 노출되어 발생해요. 백신과 특이적 치료제가 없고 치명률이 약 18~20%로 높아 예방이 가장 중요한 질병이에요. 2013년 국내 최초 보고 이후 매년 100~200건 이상 신고되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>SFTS 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>SFTS 증상은 진드기에 물린 후 1~2주의 잠복기를 거쳐 나타나요. 주요 증상은 38~40℃의 고열과 함께 오심·구토·설사·복통 등 소화기 증상이에요. 이와 더불어 두통·근육통·림프절 종창이 나타나고, 혈액검사에서 백혈구와 혈소판이 감소하는 것이 특징이에요. 중증으로 진행되면 신경 증상(의식장애·경련·혼수), 다발성 장기부전, 출혈 증상이 나타날 수 있어요. 고령자나 기저질환자는 중증으로 진행될 위험이 높으니 특히 주의가 필요해요.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>SFTS 치명률은 얼마나 되나요?</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>SFTS의 치명률은 약 18~20% 수준으로 상당히 높은 편이에요. 특히 고령자(60세 이상), 면역저하자, 당뇨·심장질환 등 기저질환자에서 사망 위험이 더 높아요. 중증으로 진행되면 다발성 장기부전이 발생하며 이 경우 치명률이 더욱 높아져요. 현재 SFTS에 대한 특이적 치료제와 백신이 없어 조기에 진단하고 중환자 집중치료 등 대증요법을 받는 것이 생존율을 높이는 데 중요하답니다. 야외활동 후 발열 증상이 있으면 즉시 의료기관을 방문하세요.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>SFTS는 언제 가장 많이 발생하나요?</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>SFTS는 주로 4월부터 11월 사이에 발생하며, 특히 진드기 활동이 가장 왕성한 5~10월에 집중적으로 신고돼요. 봄철 텃밭 작업이나 등산 등 야외활동 증가 시기와 맞물려 4~5월에도 발생 사례가 꾸준히 보고되고 있어요. 추수기인 9~10월에도 농작업 중 감염 사례가 많으니, 농촌 지역 거주자나 야외활동이 많은 분들은 진드기 예방수칙을 철저히 지켜주세요. 겨울에는 진드기 활동이 줄어 발생 보고가 거의 없답니다.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>SFTS는 치료제가 있나요?</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>현재 SFTS에 대한 특이적 치료제와 백신은 없어요. 치료는 발열·통증 완화, 수액 보충, 합병증 관리 등 대증치료 위주로 진행돼요. 중증의 경우 중환자실 집중치료가 필요할 수 있어요. 항바이러스제인 리바비린이 일부 사용되지만 효과는 제한적이에요. 조기에 진단하여 적극적인 지지요법을 받는 것이 생존율을 높이는 데 중요해요. 따라서 야외활동 후 1~2주 이내 원인 모를 발열·소화기 증상이 나타나면 즉시 진료를 받고 진드기 노출 여부를 의사에게 알려주세요.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>SFTS 환자와 접촉하면 감염될 수 있나요?</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>SFTS는 주로 진드기에 물려 감염되지만, 중증 환자나 사망자의 혈액·체액에 직접 노출될 경우 예외적으로 사람 간 전파가 가능해요. 일상적인 접촉(악수, 대화, 같은 공간 이용)으로는 전파되지 않아요. 환자를 간호하거나 의료기관에서 치료할 때는 장갑·가운·마스크(KF-94 또는 N-95)·고글 등 개인보호장구를 반드시 착용해야 해요. 환자 가족이나 의료진도 노출 후 발열 등 의심 증상이 나타나면 즉시 신고하고 진료를 받으세요.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SFTS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>SFTS(중증열성혈소판감소증후군)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>SFTS가 의심되면 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>진드기에 물린 후 또는 야외활동 후 1~2주 이내에 38℃ 이상 고열, 구역·구토·설사 등 소화기 증상이 나타나면 SFTS를 의심할 수 있어요. 이런 경우 즉시 가까운 의료기관에 방문해 진드기 노출 여부와 야외활동 이력을 의료진에게 알려주세요. 혈액검사에서 백혈구·혈소판 감소가 확인되면 SFTS 확진검사(PCR 등)를 받게 돼요. 진드기에 물린 부위를 알고 있다면 진드기를 제거한 후 보관해 두면 진단에 도움이 될 수 있어요. 늦지 않게 치료받는 것이 무엇보다 중요해요.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증이란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 쯔쯔가무시균(Orientia tsutsugamushi)에 감염된 털진드기 유충에 물려 발생하는 급성 발열성 질환이에요. 털진드기 유충은 풀밭·잡목 지역에 서식하며, 사람의 피부에 붙어 체액을 빨며 균을 옮겨요. 국내에서 가장 흔한 리케차 질환으로, 매년 5,000~8,000건 이상 신고되는 3급 법정감염병이에요. 주로 가을철(9~11월)에 집중 발생하며, 항생제(독시사이클린) 치료 시 빠르게 호전되는 것이 특징이랍니다.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 잠복기(약 10일 이내) 후 갑작스러운 발열·오한·두통으로 시작해요. 이후 근육통·기침·구토·복통·인후염이 나타나고, 발진과 가피(딱지, eschar)가 생기는 것이 큰 특징이에요. 발진은 감염 3~7일 후 몸통에서 시작해 팔다리로 퍼지는 가렵지 않은 붉은 점 형태예요. 가피는 털진드기에 물린 자리에 생기는 검은 딱지로, 쯔쯔가무시증 환자의 약 97%에서 확인되는 중요한 진단 단서예요. 증상 초기에 항생제를 투여하면 48시간 내 열이 내려가는 경우가 많아요.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>가피(딱지)가 생기면 쯔쯔가무시증인가요?</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>가피(eschar)는 쯔쯔가무시증의 가장 중요한 진단 단서 중 하나예요. 털진드기 유충이 물고 간 자리에 검은 딱지처럼 생기는데, 주로 사타구니·겨드랑이·목 뒤·배꼽 주변 등 피부가 접히는 부위에서 발견돼요. 약 97%의 쯔쯔가무시증 환자에서 확인되며, 가피와 함께 발열·두통·발진이 동반되면 쯔쯔가무시증을 강하게 의심할 수 있어요. 단, 가피만으로 확진되지는 않으며, 혈액검사나 PCR 등 확인 검사가 필요해요. 가피가 발견되면 즉시 의료기관을 방문해 주세요.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 언제 가장 많이 발생하나요?</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 털진드기 유충이 왕성하게 활동하는 9~11월에 집중 발생해요. 특히 11월에 전체 환자의 50% 이상이 발생할 정도로 가을철에 급격히 증가해요. 추수철 논밭 작업·야외 활동이 증가하는 시기와 맞물려 발생이 늘어나는 경향이 있어요. 2024년에는 11월 중순 기준 약 3,028명이 신고되었어요. 가을 야외활동 전에 예방수칙을 꼭 확인하고, 귀가 후에는 반드시 샤워하며 온몸을 살펴보세요.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 어떻게 치료하나요?</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 항생제 치료로 빠르게 회복할 수 있어요. 주로 독시사이클린(성인 기준 100mg, 1일 2회)을 처방하며, 열이 내린 후에도 최소 3일 이상 총 7일 내외로 복용해요. 대부분 항생제 투여 후 24~48시간 내에 열이 떨어져요. 임신부나 소아에게는 아지스로마이신을 사용할 수 있어요. 치료를 받지 않으면 간질성 폐렴·급성호흡곤란증후군·심근염·신부전 등 심각한 합병증이 생길 수 있어요. 국내 치명률은 약 0.1~0.3%로 낮지만, 초기 치료가 매우 중요합니다.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증 다발 지역은 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증을 매개하는 털진드기는 우리나라 전역에 분포해 전국 어디서나 발생할 수 있어요. 다만 농촌 지역, 특히 논·밭·과수원·텃밭이 많은 충남·전남·경남·경북·강원 등 지역에서 비교적 많이 발생하는 경향이 있어요. 최근에는 도시 인근 텃밭 작업, 등산 등으로 도시 거주자의 감염도 증가하고 있어요. 어디서든 가을철 야외활동 시에는 긴 옷 착용과 기피제 사용 등 예방수칙을 철저히 지켜주세요.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 재발할 수 있나요?</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>쯔쯔가무시증은 한 번 감염되어도 완전한 면역이 생기지 않아 재감염이 가능해요. 쯔쯔가무시균은 균주가 다양하게 존재해, 다른 균주에 의한 재감염이 일어날 수 있어요. 따라서 한 번 감염된 후 완치된 분도 가을철 야외활동 시 동일한 예방수칙을 철저히 지켜야 해요. 항생제 치료 후 증상이 완전히 사라졌더라도 다음 가을에 다시 감염될 수 있으니, 야외활동 후 의심 증상이 나타나면 재감염 가능성을 생각하고 즉시 진료를 받으세요.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열이란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열은 뎅기 바이러스(DENV1~4, 4가지 혈청형)에 감염된 이집트숲모기 또는 흰줄숲모기에 물려 발생하는 급성 열성 바이러스 질환이에요. 열대·아열대 지역(동남아시아·중남미·아프리카 등 100여 개국 이상)에서 유행하며, 전 세계적으로 매년 수억 명이 감염되는 중요한 감염병이에요. 국내에서는 토착 발생 없이 해외 유입 사례만 보고되며, 현재 국내 상용화된 뎅기 백신은 없어요. 예방의 핵심은 유행 지역 여행 시 모기에 물리지 않는 것이랍니다.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열은 모기에 물린 후 4~7일(최대 14일) 잠복기를 거쳐 갑작스럽게 39~40℃의 고열과 함께 심한 두통·안구통·근육통·관절통이 나타나요. '뼈가 부러지는 것 같은 통증'이라 해서 '골절열(breakbone fever)'이라고도 불려요. 발열 2~5일 후 몸통에서 팔다리로 퍼지는 발진이 나타날 수 있어요. 대부분 1~2주 내 회복되지만, 일부는 혈소판 감소로 인한 출혈 증상(잇몸 출혈·코피·점상 출혈)이 나타나는 중증 뎅기열로 진행될 수 있어 주의가 필요해요.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열 유행 국가는 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열은 동남아시아(태국·베트남·인도네시아·필리핀·말레이시아 등), 남아시아(인도·방글라데시·스리랑카 등), 중남미(브라질·콜롬비아·멕시코 등), 아프리카 열대 지역 등 약 100여 개국 이상에서 유행하고 있어요. 2024년에는 브라질 등 중남미와 동남아시아에서 역대급 유행이 보고되기도 했어요. 여행 전 '해외감염병 NOW'(해외감염병now.kr)에서 방문 국가의 최신 감염병 발생 정보를 꼭 확인하세요.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열 재감염이 왜 위험한가요?</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>뎅기 바이러스는 혈청형이 4가지(DENV1~4)가 있어요. 한 혈청형에 감염된 후 회복되면 그 혈청형에 대한 평생 면역이 생기지만, 나머지 3가지 혈청형에 대한 면역은 생기지 않아요. 문제는 다른 혈청형에 재감염될 경우 항체의존성 감염 증강(ADE) 현상으로 인해 중증 뎅기열(뎅기 출혈열·뎅기 쇼크 증후군)로 진행될 위험이 훨씬 높아져요. 중증 뎅기열은 생명을 위협할 수 있으므로, 이전에 뎅기열에 걸렸던 분은 유행 국가 여행 시 특히 모기 예방에 더욱 철저해야 해요.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열 치료법이 있나요?</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>현재 뎅기열에 특효인 항바이러스제는 없어요. 치료는 충분한 수분 섭취, 해열제(아세트아미노펜) 복용, 안정 등 대증치료 위주로 진행해요. 아스피린이나 이부프로펜 등 비스테로이드 소염제(NSAIDs)는 출혈 위험을 높일 수 있어 사용하면 안 돼요. 혈소판이 심하게 감소하거나 출혈 증상이 나타나는 중증 뎅기열은 입원 치료가 필요해요. 조기에 적절한 치료를 받으면 사망률을 크게 낮출 수 있어요. 귀국 후 의심 증상이 있으면 즉시 의료기관에서 해외여행력을 알리고 진료를 받으세요.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>뎅기열</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>귀국 후 뎅기열이 의심될 때 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>뎅기열 유행 국가 여행 후 귀국 시 입국장 검역관에게 증상을 알리고 건강 상태 질문서를 제출해 주세요. 귀국 후 2주 이내 38℃ 이상 발열·심한 두통·근육통·발진 등 의심 증상이 나타나면 즉시 의료기관을 방문해 방문 국가와 여행 기간을 알려주세요. 국립검역소나 일부 보건소에서 무료 뎅기열 검사를 받을 수 있어요. 회복 후 최소 4주간은 헌혈을 삼가고, 모기에 물리지 않도록 주의해 2차 전파를 예방해 주세요.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>라임병</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>라임병이란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>라임병은 보렐리아균(Borrelia burgdorferi 등)에 감염된 참진드기에 물려 발생하는 세균성 감염병이에요. 진드기가 피부에 붙어 흡혈하는 과정(최소 36~48시간 이상)에서 균이 전파돼요. 국내에서는 1993년 최초 보고 이후 2023년 기준 연간 45건 내외의 소수 사례가 신고되고 있어요. 미국·유럽·아시아 등 넓은 지역에서 발생하는 가장 흔한 진드기매개질환 중 하나예요. 조기에 발견해 항생제 치료를 받으면 완치가 가능하지만, 진단이 늦어지면 신경계·심장·관절 등에 합병증이 생길 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>라임병</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>라임병 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>라임병 증상은 3단계로 나뉘어요. 초기(1기)에는 진드기에 물린 후 3~30일 내에 물린 자리 주변에 과녁 모양의 이동성 홍반(EM)이 나타나고, 발열·피로·두통·근육통이 동반될 수 있어요. 수주~수개월 후 2기에는 심장 두근거림·전도 장애, 안면 신경 마비, 뇌수막염 등 신경계·심장 증상이 나타날 수 있어요. 치료 받지 않은 경우 수개월~수년 후 3기(후기)에는 무릎 등 대관절의 관절염이 생길 수 있어요. 초기 증상에서 발견해 치료하면 가장 좋은 예후를 보여요.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>라임병</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>라임병 이동성 홍반이란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>이동성 홍반(Erythema Migrans, EM)은 라임병의 가장 중요한 초기 증상이에요. 진드기에 물린 자리에서 시작해 점점 바깥쪽으로 확장되는 붉은 발진으로, 중심부가 점차 맑아지면서 지름 5~70cm(평균 15cm 이상)까지 커지는 '황소 눈(bull's-eye)' 또는 과녁 모양이 특징이에요. 물린 후 보통 7~14일(3~30일) 이내에 나타나며, 사타구니·겨드랑이·무릎 뒤 등 피부가 접히는 곳에 잘 생겨요. 이동성 홍반이 보이면 즉시 의료기관을 방문해 라임병 검사를 받으세요.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>라임병</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>라임병은 어떻게 치료하나요?</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>라임병은 항생제로 치료해요. 초기(이동성 홍반 단계)에는 독시사이클린(200mg/일, 2회/일) 또는 아목시실린·세푸록심을 10~21일 경구 투여해요. 뇌수막염·심근염 등 중증 합병증이 있는 경우 세프트리악손 등을 2~4주간 정맥 투여해요. 관절염에는 4주간 항생제 치료를 하고, 신경 증상이 동반된 경우 정맥 투여를 고려해요. 조기에 치료하면 대부분 완치되지만, 진단이 늦어지면 일부에서 피로감·근골격계 통증·신경계 증상이 오래 지속될 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>라임병</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>라임병은 국내에도 있나요?</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>네, 라임병은 국내에서도 발생해요. 1993년 국내 첫 증례가 보고된 이후 꾸준히 산발적으로 발생하고 있으며, 2023년 기준 연간 45건 내외가 신고됐어요. 국내 추정 감염지역은 충남·인천·서울·강원·전남 등이에요. 국내 발생 건수는 미국·유럽에 비해 적지만, 야산·숲·풀밭에서 활동하는 경우 진드기에 물려 감염될 수 있어요. 등산·캠핑·텃밭 작업 등 야외활동 후 진드기에 물린 부위 주변에 붉은 발진이 나타나면 즉시 의료기관을 방문하세요.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염(TBE)이란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염(Tick-Borne Encephalitis, TBE)은 TBE 바이러스에 감염된 참진드기에 물려 발생하는 바이러스성 뇌염이에요. 유럽형·시베리아형·극동형 3가지 아형이 있으며, 아형에 따라 임상 양상과 치명률이 다소 달라요. 극동형은 치명률이 20~40%로 높고, 유럽형은 상대적으로 낮아요. 현재 특이적 항바이러스 치료제는 없으며, 대증치료 및 합병증 관리로 치료해요. 유행 지역 여행자는 예방접종을 고려할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염 유행 지역은 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염은 유럽 중부·동부(오스트리아·독일·체코·스위스·러시아 등)와 아시아 북부·동부(러시아 시베리아·중국 북동부·일본 홋카이도 등)에서 주로 유행해요. 국내에서는 드물게 보고되지만 러시아 극동 지역 여행자에서 감염 사례가 있어요. 유럽 등 유행 지역으로 장기 여행하거나 야외 활동(등산·캠핑·사냥 등)을 계획하는 경우 출발 전 예방접종 여부를 확인하는 것이 좋아요. 여행 전 '해외감염병 NOW'에서 최신 유행 정보를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염 예방접종이 있나요?</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>네, 진드기매개뇌염(TBE) 예방백신이 있어요. 유럽에서 개발된 백신(FSME-Immun, Encepur 등)이 유럽형 및 시베리아형에 효과적이에요. 기본 접종은 3회(0·1~3개월·5~12개월)이며, 이후 3~5년마다 추가접종을 권고해요. 빠른 방어가 필요한 경우 단축 일정으로 접종할 수 있어요. 유행 지역(러시아·동유럽·중앙아시아 등) 장기 여행자나 야외 활동이 많은 경우 예방접종이 권장돼요. 현재 국내에서는 일부 해외여행 클리닉에서 수입 백신을 접종할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>라임병·기타진드기매개</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>진드기매개뇌염은 두 단계로 나뉘어 증상이 나타나는 경우가 많아요. 1단계(약 1~8일)는 독감 유사 증상으로 발열·두통·근육통·피로감이 나타나다가 일시적으로 회복돼요. 이후 약 1~3주 후 2단계로 뇌·수막 침범 증상인 고열·심한 두통·구역·구토·경부 강직·의식 변화·마비 등이 나타나요. 중증의 경우 영구적인 신경학적 후유증(마비·인지장애)이 남을 수 있어요. 극동형은 유럽형보다 중증도가 높아 치명률이 20~40%로 높아요. 진단은 혈청 또는 뇌척수액에서 특이 항체 또는 바이러스를 검출해 확인해요.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열이란 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열은 웨스트나일 바이러스(West Nile Virus)에 감염된 Culex속 모기에 물려 발생하는 모기매개 바이러스 감염병이에요. 자연계에서 모기와 조류 사이에 순환하다 사람에게 전파돼요. 감염자의 약 80%는 증상이 없고, 20% 정도에서 가벼운 열성 질환이 생기며, 약 1% 미만에서 뇌염·수막염 등 심각한 신경계 합병증이 발생해요. 인체용 백신과 특이적 치료제는 없어요. 국내 토착 발생은 없으며 해외여행 유입 사례로만 보고되고 있어요.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열 증상이 어떻게 되나요?</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열의 증상은 감염자의 약 80%에서 무증상으로 지나가요. 증상이 있는 경우(20%) 발열·두통·피로감·근육통·발진·림프절 종창 등 가벼운 독감 유사 증상이 2~7일간 나타나다 자연 회복돼요. 그러나 약 1% 미만(주로 고령자·면역저하자)에서 뇌염·수막염·급성 이완성 마비 등 심각한 신경계 합병증이 발생하며, 이 경우 치명률이 3~15%에 달할 수 있어요. 신경계 합병증 발생 후 완전히 회복되지 않고 장기 후유증이 남는 경우도 있어요.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열 유행 지역은 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열은 아프리카(사하라 이남)에서 처음 발견되었으며, 현재 미국·캐나다 등 북미, 유럽(이탈리아·그리스·루마니아 등), 중동, 아시아(이스라엘·러시아 등) 등 광범위한 지역에서 유행하고 있어요. 특히 미국에서는 1999년 뉴욕 침입 후 매년 수천 건의 신경계 합병증 사례가 보고되는 주요 모기매개감염병이 되었어요. 유행 지역 방문 시에는 모기 기피제 사용 및 긴 옷 착용 등 예방수칙을 철저히 지켜주세요.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열 치료제가 있나요?</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>현재 웨스트나일열에 대한 특이적 항바이러스 치료제와 인체용 백신은 없어요. 치료는 충분한 수분 섭취, 안정, 해열진통제 투여 등 대증치료 위주로 진행해요. 신경계 합병증(뇌염·수막염)이 발생한 중증의 경우 입원하여 집중 지지치료를 받아야 해요. 말(馬)을 위한 백신은 있지만 인체용은 아직 개발 중이에요. 예방이 최선이므로 유행 지역 방문 시 모기에 물리지 않도록 기피제 사용, 긴 옷 착용, 방충망 사용 등을 철저히 해 주세요.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>모기 예방</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>모기에 물리지 않으려면 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>모기 예방의 핵심은 노출을 최소화하는 것이에요. 모기가 활발한 4~10월 야간(일몰 후~일출 전)에는 야외 활동을 자제해 주세요. 외출 시에는 밝은색 긴 소매·긴 바지를 착용하고, 피부 노출 부위에 모기 기피제를 뿌려 주세요. 실내에서는 방충망을 정비하고 에어컨이나 선풍기를 사용해 모기 접근을 줄여 주세요. 모기장을 사용하면 더욱 효과적이에요. 귀가 후에는 반드시 샤워하고 옷을 세탁해 주세요. 말라리아 위험지역이라면 보건소에서 무료 진단을 받을 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>모기 예방</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>모기 기피제를 올바르게 사용하는 방법은 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>모기 기피제는 피부 노출 부위에 골고루 얇게 펴 발라 주세요. 얼굴에는 직접 뿌리지 말고 손에 덜어 눈·입·코를 피해 바르세요. 스프레이형은 실내보다 야외에서 사용하고 흡입하지 않도록 주의하세요. 기피제 사용 후 야외에서 돌아오면 비누로 깨끗이 씻어 내세요. 지속시간은 성분·농도에 따라 다르므로, 장시간 야외활동 시 3~4시간 간격으로 재도포해 주세요. 어린이에게 사용 시에는 어른이 손에 덜어 발라 주고, 아이 손이 닿는 손바닥 부위는 바르지 마세요.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>모기 예방</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>DEET 성분 기피제는 어린이에게 안전한가요?</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>DEET 성분 기피제는 만 12세 이상의 어린이와 성인에게 사용 권장돼요. 일부 제품은 생후 2개월 이상부터 사용 가능하나, 어린이의 경우 30% 이하 저농도 제품을 사용하는 것이 좋아요. 영아(6개월 미만)에게는 사용을 피하세요. 어린이에게는 DEET 대신 이카리딘(피카리딘) 또는 IR3535 성분의 기피제가 더 안전한 대안이 될 수 있어요. 이카리딘은 생후 6개월 이상, IR3535는 생후 6개월 이상에서 사용 가능해요. 기피제 선택 전 반드시 제품 라벨의 연령 기준을 확인하고, 사용 후에는 비누로 씻어 주세요.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>모기 예방</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>모기는 언제 가장 활발히 활동하나요?</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>국내 말라리아를 매개하는 얼룩날개모기는 주로 야간(일몰 직후~일출 직전)에 활발히 활동해요. 뎅기열·지카 바이러스를 매개하는 흰줄숲모기(Aedes albopictus)는 낮에도 활동하는 주행성이에요. 계절적으로는 모기가 4~10월에 활발하며, 기온 25~30℃, 습도가 높은 환경에서 번식과 활동이 왕성해요. 새벽~이른 아침과 저녁~밤 시간대에 야외활동을 줄이고, 그 시간대에는 반드시 기피제를 사용하고 긴 옷을 착용하세요.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>모기 예방</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>집 주변 모기를 줄이는 방법이 있나요?</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>모기 유충은 고인 물에서 자라므로, 집 주변 고인 물을 없애는 것이 가장 효과적인 방법이에요. 화분 받침대·폐타이어·빈 그릇·물통 등에 물이 고이지 않도록 정기적으로 비워 주세요. 방충망에 찢어진 곳이 없는지 점검하고 보수해 주세요. 하수구·배수로 정비도 중요해요. 실내에는 모기향·전자 모기기 등을 사용하고, 취침 시에는 모기장을 사용하면 효과적이에요. 풀숲·수풀이 우거진 곳은 벌초 등으로 정리해 모기 서식처를 줄이는 것도 도움이 돼요.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>모기 예방</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>해외여행 시 모기 예방은 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>해외여행 전 방문 국가의 감염병 발생 현황을 '해외감염병 NOW'(해외감염병now.kr)에서 확인하세요. 말라리아 유행 국가를 방문할 경우 출발 4주 전 여행의학 클리닉에서 예방약을 처방받으세요. 여행 중에는 밝은색 긴 소매·긴 바지를 착용하고, 모기 기피제를 3~4시간 간격으로 재도포하세요. 숙소 내 에어컨이 없는 경우 모기장을 사용하고, 창문·문에 방충망이 없으면 기피제를 더 자주 사용하세요. 귀국 후 2주 이내 의심 증상이 나타나면 즉시 의료기관에 방문해 여행 이력을 알려주세요.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>진드기에 물리지 않으려면 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>야외활동 시 진드기 예방을 위해 긴 소매·긴 바지를 착용하고, 바지단을 양말이나 장화 안으로 넣어 피부 노출을 최소화하세요. 밝은색 옷을 입으면 진드기를 발견하기 쉬워요. 진드기 기피제(DEET·이카리딘 성분)를 옷과 피부 노출 부위에 발라 주세요. 풀숲·덤불·낙엽 더미에 앉거나 눕지 말고, 풀밭에 앉을 때는 돗자리를 사용하세요. 야외활동 후에는 옷을 뒤집어 진드기를 확인하고 즉시 세탁해 주세요.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>야외활동 후 진드기 확인은 어떻게 하나요?</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>야외활동 후 귀가 즉시 샤워하며 온몸을 꼼꼼히 확인해 주세요. 진드기는 작게는 1mm 이하로 매우 작아 육안으로 찾기 어려울 수 있어요. 특히 진드기가 숨기 좋아하는 두피·귀 뒤·목·겨드랑이·사타구니·무릎 뒤·발목 등 피부 접히는 곳을 집중 점검하세요. 머리카락 속도 손가락으로 꼼꼼히 훑어보세요. 야외활동에서 입은 옷은 집 안으로 가져오기 전 잘 털고 즉시 세탁기에 돌려 주세요. 가능하면 귀가 즉시 샤워하는 것이 가장 좋아요.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>진드기가 피부에 붙었을 때 어떻게 제거하나요?</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>진드기가 피부에 붙었을 때는 핀셋이나 진드기 제거 전용 도구를 사용해 피부 표면에 가깝게 잡고 천천히 수직으로 당겨내세요. 당길 때 비틀거나 짓이기지 마세요. 손으로 맨손 제거, 바셀린·오일·성냥·불 사용은 진드기가 체액을 역류시켜 감염 위험을 높일 수 있어 절대 금지예요. 제거 후 물린 부위와 손을 비누로 깨끗이 씻고 소독하세요. 제거한 진드기는 버리지 말고 비닐봉지에 보관해 두면 진단에 도움이 될 수 있어요. 이후 발열 등 이상 증상이 나타나면 즉시 의료기관을 방문하세요.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>진드기에 물린 후 얼마나 지나면 증상이 나타나나요?</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>진드기에 물린 후 증상이 나타나는 시기는 질병마다 달라요. SFTS는 물린 후 1~2주(6~14일), 쯔쯔가무시증은 10일 이내, 라임병은 3~30일(이동성 홍반), 진드기매개뇌염은 4~28일이에요. 잠복기 동안에는 대부분 아무런 증상이 없어요. 따라서 진드기에 물린 경우 물린 날짜와 장소를 기록해 두고, 잠복기 내에 발열·두통·발진·근육통 등 이상 증상이 나타나면 즉시 의료기관을 방문해 진드기 노출 이력을 알려주세요.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>농작업 중 진드기 감염을 예방하려면 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>농작업 중 진드기 감염 예방을 위해 긴 소매·긴 바지·장갑·장화를 착용하고, 바지단을 양말 안으로 넣어 주세요. 작업 전 피부 노출 부위와 옷에 진드기 기피제를 뿌리고, 2~4시간마다 재도포하세요. 풀 위에 앉아 휴식할 때는 반드시 돗자리를 깔아 주세요. 작업 중간 쉬는 시간에도 몸에 진드기가 붙지 않았는지 확인하세요. 귀가 후 즉시 샤워하며 온몸을 점검하고, 작업복은 뒤집어 털고 즉시 세탁하세요. 진드기 활동이 왕성한 9~11월에는 더욱 철저히 예방수칙을 지켜주세요.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>반려동물을 통해 진드기 감염이 될 수 있나요?</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>반려동물이 야외에서 진드기를 묻혀 올 수 있어요. 진드기가 반려동물의 털에 붙어 있다가 사람에게 이동해 물 수 있으므로 주의가 필요해요. 반려동물과 야외활동 후에는 반드시 동물의 털을 손가락으로 천천히 훑어 진드기가 붙어있는지 확인하세요. 발견된 진드기는 핀셋으로 조심스럽게 제거하고, 수의사에게 처방받은 진드기 예방약(스팟온·목걸이 등)을 정기적으로 사용하면 효과적이에요. 반려동물 접촉 후 손을 깨끗이 씻는 것도 중요해요.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>예방 수칙</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>진드기 예방</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>진드기 기피제는 어떤 것을 사용해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>진드기 예방에 효과적인 기피제 성분으로는 DEET(디에틸톨루아미드), 이카리딘(피카리딘), IR3535가 있어요. DEET는 가장 광범위하게 연구된 성분으로 진드기와 모기 모두에 효과적이며, 15% 이상 농도에서 수 시간 효과가 지속돼요. 이카리딘은 DEET보다 피부 자극이 적고 어린이·임산부에도 비교적 안전해요. 옷에 뿌리는 퍼메트린 처리 제품도 진드기 예방에 효과적이에요(피부에는 직접 사용 불가). 기피제는 2~4시간마다 재도포하고 귀가 후 씻어 내세요.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>의심 증상 및 신고</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>야외활동 후 어떤 증상이 나타나면 병원에 가야 하나요?</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>야외활동(등산·텃밭·농작업·낚시 등) 후 다음 증상이 나타나면 즉시 의료기관을 방문하세요. ▶ 38℃ 이상의 고열 ▶ 심한 두통·근육통·관절통 ▶ 오심·구토·설사 등 소화기 증상 ▶ 온몸에 붉은 발진 ▶ 피부에 검은 딱지(가피) ▶ 물린 부위 주변의 붉은 발진(이동성 홍반) ▶ 심한 피로감·의식 변화 등이에요. 증상 발현까지 수일~수주가 걸릴 수 있으므로, 활동 후 4주 이내 이상 증상이 생기면 반드시 진드기나 모기에 물린 이력, 야외활동 장소와 날짜를 의사에게 알려주세요.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>의심 증상 및 신고</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>매개체감염병은 어디서 진료를 받아야 하나요?</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>매개체감염병이 의심되면 가까운 의료기관(내과·감염내과)을 방문해 진료를 받으세요. 야외활동 이력, 진드기·모기 노출 여부, 방문 지역, 증상 발생 시점 등을 의료진에게 상세히 알려주시면 진단에 큰 도움이 돼요. 말라리아 위험지역 거주자라면 가까운 보건소에서도 무료로 검사와 진료를 받을 수 있어요. 해외여행 후 감염이 의심되는 경우 국립중앙의료원 중앙감염병병원, 국립검역소, 또는 대학병원 감염내과를 방문하는 것이 좋아요. 증상이 심하거나 응급 상황이라면 119에 신고하거나 응급실을 이용하세요.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>의심 증상 및 신고</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>의료인이 매개체감염병을 신고하는 방법은 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>의료인은 매개체감염병 환자(의사환자 포함)를 진단했을 때 법정감염병 신고 의무가 있어요. 신고 방법은 질병보건통합관리시스템(is.cdc.go.kr)에 온라인으로 입력하거나, 팩스·우편으로 관할 보건소에 신고할 수 있어요. 신고 기한은 SFTS·말라리아·뎅기열 등 2급 감염병은 24시간 이내, 쯔쯔가무시증·라임병 등 3급 감염병은 24시간 이내예요. 신고 서식은 질병보건통합관리시스템 또는 질병관리청 홈페이지에서 내려받을 수 있어요. 미신고 시 「감염병의 예방 및 관리에 관한 법률」에 따라 과태료가 부과될 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://is.cdc.go.kr</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>의심 증상 및 신고</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>질병관리청 1339 콜센터는 어떤 경우에 전화하나요?</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>질병관리청 1339 콜센터는 24시간 365일 운영되는 감염병 관련 종합 상담 전화예요. ▶ 매개체감염병 의심 증상이 있을 때 ▶ 진드기·모기에 물린 후 어떻게 해야 할지 모를 때 ▶ 해외여행 전 방문 국가 감염병 정보가 필요할 때 ▶ 말라리아 예방약 복용 방법이나 부작용이 궁금할 때 ▶ 가까운 검사 가능 의료기관이나 보건소를 안내받고 싶을 때 등에 이용할 수 있어요. 감염병 신고·의심 신고, 해외 여행 건강 상담도 1339로 하면 된답니다.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>의심 증상 및 신고</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>매개체감염병 진단 검사는 어디서 받나요?</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>매개체감염병 의심 시 가까운 의료기관 또는 보건소에서 혈액 검사를 받을 수 있어요. 말라리아 위험지역 보건소에서는 신속진단검사(RDT)를 무료로 받을 수 있어요. SFTS·쯔쯔가무시증 등 진드기매개감염병은 혈액으로 PCR(유전자검출)·항체검사 등을 통해 확진해요. 보건소에서 검체를 채취해 시도 보건환경연구원 또는 질병관리청에 의뢰하는 방식으로 검사가 이루어져요. 뎅기열 등 해외유입 감염병 검사는 국립검역소 또는 국립중앙의료원에서 가능해요. 의심 증상이 있으면 지체하지 말고 의료기관을 방문하세요.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>의심 증상 및 신고</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>해외여행 후 귀국 시 건강 신고는 어떻게 하나요?</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>해외 감염병 유행 국가에서 귀국할 때 공항·항만 입국장 검역대에서 건강 상태 질문서를 작성·제출해 주세요. 발열·기침·설사 등 의심 증상이 있거나, 말라리아·뎅기열 등 감염병 유행 지역을 방문했다면 검역관에게 즉시 알려야 해요. 귀국 후 증상이 없더라도 잠복기(질병마다 다름) 이내에 증상이 생기면 즉시 가까운 의료기관을 방문해 해외여행 이력을 반드시 알려주세요. 자세한 귀국 후 건강 관리 정보는 '해외감염병 NOW'(해외감염병now.kr)에서 확인할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>위험지역 및 발생 동향</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>국내 말라리아 위험지역 53개 시군구는 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>2024년 기준 국내 말라리아 위험지역은 서울(13개구: 강북·도봉·노원·성북·강서·은평·서대문·마포·종로·중·동대문·성동·광진구), 경기(22개 시군: 고양·파주·김포·양주·동두천·의정부·남양주·구리·하남·광주·성남·수원·안양·부천·광명·시흥·안산·군포·의왕·오산·화성·용인), 인천(10개 구·군: 강화·옹진·계양·부평·남동·연수·미추홀·중·동·서구), 강원(8개 시군: 철원·화천·양구·인제·춘천·홍천·횡성·원주) 등 4개 시·도 내 53개 시군구예요. 위험지역 거주자는 말라리아 의심 증상 발생 시 가까운 보건소를 방문해 주세요.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>위험지역 및 발생 동향</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>국내 SFTS 다발 지역은 어디인가요?</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>SFTS는 작은소참진드기가 서식하는 전국 야산·농촌 지역에서 발생하며, 특정 지역에 집중되기보다 전국에 걸쳐 산발적으로 발생해요. 다만 농작업이 많고 야외 활동이 잦은 경남·전남·경북·충남·강원 등 농촌 지역에서 상대적으로 많이 보고되는 경향이 있어요. 2025년에도 5월~10월 사이에 사망자를 포함한 확진 사례가 지속 보고되고 있어요. 전국 어디서나 야산·풀밭·농경지 활동 시 진드기 예방수칙을 철저히 지키는 것이 가장 중요합니다.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>위험지역 및 발생 동향</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>매개체감염병 발생 동향은 어디서 확인하나요?</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>국내 매개체감염병 발생 동향은 질병관리청 공식 홈페이지(kdca.go.kr)에서 확인할 수 있어요. 질병관리청은 주간 감염병 발생 현황 보고서, 감염병 포털, 감염병 통계 현황 등을 정기 발표하고 있어요. 또한 말라리아의 경우 매개모기 밀도 감시 결과에 따라 '말라리아 주의보·경보'를 발령하며, 이 정보도 질병관리청 홈페이지에서 확인 가능해요. 해외 감염병 유행 정보는 '해외감염병 NOW'(해외감염병now.kr)를 통해 최신 국가별 발생 현황을 확인할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>위험지역 및 발생 동향</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>해외 감염병 유행 정보는 어디서 확인하나요?</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>해외 감염병 유행 정보는 질병관리청이 운영하는 '해외감염병 NOW'(해외감염병now.kr)에서 국가별·질병별 최신 유행 현황, 여행 주의 정보, 예방수칙을 한눈에 확인할 수 있어요. 외교부 해외안전여행 홈페이지(0404.go.kr)에서도 국가별 감염병 안전 정보를 제공해요. 세계보건기구(WHO)와 미국 CDC 홈페이지도 국제적인 유행 정보를 제공하는 신뢰할 수 있는 출처예요. 여행 전 반드시 이 정보들을 확인하고, 필요한 경우 여행의학 클리닉에서 상담받으세요.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>http://해외감염병now.kr</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>위험지역 및 발생 동향</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>매개체감염병 주의보·경보는 어떻게 발령되나요?</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>질병관리청은 말라리아를 포함한 주요 매개체감염병에 대해 주의보·경보 발령 제도를 운영해요. 말라리아의 경우 위험지역 내 61개 지점에서 매개 얼룩날개모기를 주기적으로 채집·감시하다가, 하루 평균 모기지수가 기준(0.5 이상)을 충족하는 지역이 3개소 이상이면 주의보를, 더 높은 밀도가 확인되면 경보를 발령해요. 경보가 발령되면 해당 지역 주민에게 예방수칙 강화 및 의심 증상 시 즉각 진료 등을 안내해요. 발령 정보는 질병관리청 홈페이지, 보도자료, 지역 보건소 등을 통해 공지돼요.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>예방수칙</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>반려동물</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>반려동물과 산책 시 진드기 감염(SFTS)을 예방하려면 어떻게 하나요?</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>반려동물 산책 시 진드기 방지 옷을 입히거나 기피제를 사용하고 가급적 풀숲을 피하는 것이 좋아요. 외출 후에는 귀 안쪽, 발가락 사이, 가슴 아랫부분 등 진드기가 잘 붙는 부위를 꼼꼼히 확인해 주세요. 진드기를 발견했다면 맨손으로 만지지 말고 핀셋 등 제거 도구를 사용해 피부에 가깝게 잡아 떼어내야 하며, 제거 후 동물병원 진료를 권장해요.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>헌혈</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 위험지역을 방문했는데 헌혈이 가능한가요?</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 국내 헌혈제한지역에 1박 이상 숙박(거주 또는 군복무 포함)한 경우, 1년간 전혈 및 혈소판 성분 헌혈을 할 수 없으며 혈장 성분 헌혈만 가능해요. 말라리아 위험지역에서 벗어난 후 발열 등 의심 증상이 발생하면 즉시 가까운 병원을 찾아 의사에게 방문 이력을 알리고 진료를 받아주세요.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://bloodinfo.net</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>혈액관리본부 확인</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>진료 및 치료</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 약을 먹고 토했는데 다시 먹어야 하나요?</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 약 복용 후 30분 이내에 구토를 했다면 약물이 제대로 흡수되지 않았을 가능성이 있어 다시 복용하는 것을 권장해요. 하지만 복용 후 30분이 지난 이후에 구토했다면 약물이 충분히 흡수된 것으로 보아 다시 드시지 않아도 됩니다. 구토가 심할 경우 의료기관을 방문해 항구토제 처방 등을 상담해 보세요.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>말라리아</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>진료 및 치료</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 치료가 끝났는데도 계속 피곤해요. 후유증인가요?</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>말라리아 치료 후에도 수일에서 수주 간 피로감이나 무기력증이 계속되는 경우가 있어요. 이는 감염 기간 동안 발생한 염증에 대한 몸의 자연스러운 회복기 반응일 수 있습니다. 보통 시간이 지나면 호전되지만, 증상이 너무 길어지거나 일상생활이 힘들다면 병원을 다시 방문해 진료를 받아보시는 것이 좋습니다.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>모기매개감염병</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>해외유입</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>해외여행 시 모기매개감염병(뎅기열, 지카 등)을 예방하려면?</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>여행 전 방문할 국가의 감염병 발생 정보를 미리 확인하세요! 여행 중에는 밝은색 긴팔과 긴바지를 입어 피부 노출을 최소화하고, 모기 기피제를 꼼꼼히 발라주세요. 방충망이나 모기장이 있는 숙소를 이용하는 것도 중요합니다. 귀국 후 2주 이내에 발열, 발진, 두통 등이 나타나면 즉시 1339에 전화하거나 의료기관을 방문해 여행력을 꼭 알려주세요.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>해외감염병NOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>인수공통감염병</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>개요</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>인수공통감염병이 무엇이고 어떻게 예방하나요?</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>인수공통감염병은 사람과 동물 사이에서 서로 전파되는 병원체에 의해 발생하는 감염병이에요. 예방을 위해서는 야생동물이나 유기동물과의 직접적인 접촉을 피하고, 농작업이나 야외 활동 시 오염된 물이나 토양에 피부가 닿지 않도록 장화, 장갑 등 보호장구를 반드시 착용해야 합니다. 작업 후에는 꼭 깨끗하게 샤워해 주세요.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>진드기설치류 매개</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>진단 및 관리</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
           <t>쯔쯔가무시증이나 신증후군출혈열 환자와 접촉해도 괜찮나요?</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>네, 괜찮습니다. 쯔쯔가무시증이나 중증열성혈소판감소증후군(SFTS)과 같은 진드기 매개 감염병이나 신증후군출혈열 등 설치류 매개 감염병은 일반적으로 사람 간 직접 전파가 되지 않으므로, 환자를 별도로 격리하거나 접촉자를 따로 관리할 필요는 없어요. (단, 체액 및 혈액 노출은 주의해야 합니다)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kdca.go.kr</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>자세히 보기</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>모기매개감염병</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>치쿤구니야열</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>치쿤구니야열은 어떻게 감염되고 어떤 증상이 있나요?</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>치쿤구니야열은 감염된 숲모기(흰줄숲모기, 이집트숲모기 등)에 물려 감염돼요. 급성 발열과 함께 심한 관절통, 두통, 근육통, 발진 등이 나타납니다. 예방 백신이나 치료제가 없으므로, 유행 지역(동남아, 아프리카 등) 방문 시 모기에 물리지 않는 것이 가장 중요해요!</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>해외감염병NOW</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>모기매개감염병</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>지카바이러스</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>지카바이러스 감염증 유행 국가에 다녀왔는데 임신을 계획해도 될까요?</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>지카바이러스 감염증은 모기뿐만 아니라 성접촉을 통해서도 감염될 수 있으며, 임신부가 감염되면 태아 소두증을 유발할 수 있어요. 발생 국가를 방문한 남녀 모두 귀국 후 최소 3개월간은 임신을 연기하고 콘돔을 사용하거나 금욕해야 합니다.</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>모기매개감염병</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>웨스트나일열</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열은 어떤 병인가요? 우리나라에도 있나요?</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>웨스트나일열은 감염된 조류의 피를 빤 집모기류에 물려 감염되는 질환이에요. 다행히 아직 국내 발생 사례는 없고 모두 해외(주로 미국, 유럽, 아프리카, 중동) 유입 사례입니다. 약 80%는 무증상이지만, 심하면 뇌염 등을 일으킬 수 있으니 해외여행 시 모기를 조심하세요!</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>모기매개감염병</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>황열</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>아프리카나 중남미 여행 시 황열 예방접종을 꼭 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>네, 아프리카와 중남미 42개국은 황열 위험국가로, 입국 시 황열 예방접종 증명서를 요구하는 곳이 많아요. 출국 최소 10일 전에는 반드시 국제공인 예방접종기관에서 접종을 받아야 하며, 1회 접종으로 평생 효과가 유지된답니다.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>예방접종기관 찾기</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>모기매개감염병</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>일본뇌염</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>일본뇌염은 모기에 물리면 다 걸리나요? 예방접종이 필요한가요?</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>일본뇌염 바이러스를 가진 작은빨간집모기에 물려도 99% 이상은 무증상이나 가벼운 증상으로 지나가요. 하지만 드물게 급성 뇌염으로 진행될 수 있어 주의가 필요합니다. 소아는 국가예방접종 일정에 맞춰 접종하고, 성인도 위험지역(축사 인근 등) 거주자나 유행국가 여행자라면 예방접종을 권장해요.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://nip.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>예방접종도우미</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>진드기설치류 매개</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>라임병</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>진드기에 물린 자리에 과녁 모양의 붉은 반점이 생겼어요 (라임병).</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>참진드기에 물린 뒤 1~3주 후 물린 부위를 중심으로 점점 퍼져나가는 과녁 모양의 붉은 반점(유주성 홍반)이 생겼다면 라임병을 의심해야 해요. 초기에 항생제로 쉽게 치료할 수 있으니 즉시 병원에 방문해 진드기에 물린 사실을 알려주세요!</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>진드기설치류 매개</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>렙토스피라증</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>홍수나 태풍 직후 복구 작업 시 렙토스피라증을 조심해야 하는 이유는요?</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>렙토스피라증은 감염된 동물(주로 쥐)의 소변으로 오염된 물이나 흙이 피부 상처나 점막에 닿아 감염돼요. 수해 복구, 벼 세우기 작업 등을 할 때는 반드시 장화와 고무장갑 등 보호구를 착용해 피부 노출을 막아야 합니다. 작업 후 열이 나면 꼭 진료를 받으세요!</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>신고·진료·위험지역</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>인수공통감염병</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>공수병</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>길고양이나 야생 너구리에게 물렸는데 공수병(광견병)에 걸릴 수 있나요?</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>네, 개뿐만 아니라 너구리, 오소리, 고양이, 박쥐 등 온혈동물을 통해서도 감염될 수 있어요. 동물에게 물렸다면 즉시 흐르는 물에 비누로 15분 이상 상처를 씻어내고, 바로 병원으로 가서 공수병 백신 및 면역글로불린 투여 등 응급처치를 받아야 합니다.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>인수공통감염병</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>유비저</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>동남아 여행 중 흙이나 물을 만진 후 걸릴 수 있는 유비저는 무엇인가요?</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>유비저는 열대지역(태국, 베트남 등 동남아)의 오염된 흙이나 고인 물에 피부 상처가 닿거나 호흡기로 흡입하여 감염되는 병입니다. 당뇨, 신장질환 등 기저질환자가 특히 위험하므로, 우기(비가 많이 올 때) 동남아 여행 시 흙이나 웅덩이 물과의 접촉을 피하세요.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>인수공통감염병</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>큐열</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>소, 양, 염소를 키우는 농장에서 큐열을 조심하려면 어떻게 해야 하나요?</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>큐열은 감염된 가축의 유산·출산 시 배출되는 양수나 태반, 소변 등이 먼지로 섞여 호흡기로 들어와 감염돼요. 가축의 분만이나 유산 처리를 할 때는 반드시 마스크(KF94 이상), 장갑, 장화 등 보호구를 착용해야 합니다. 또한 살균되지 않은 생우유 섭취도 피하세요.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>매개체감염병 기본정보</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>진드기설치류 매개</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>발진열/발진티푸스</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>발진열과 발진티푸스는 진드기 매개 질환인가요?</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>아니요, 두 질환 모두 벼룩과 이를 통해 전파돼요. 발진열은 주로 쥐벼룩을 통해, 발진티푸스는 사람의 몸니(louse)를 통해 감염됩니다. 주변에 쥐가 서식하지 못하게 하고 의복 세탁 등 청결한 위생 환경을 유지하는 것이 중요해요.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kdca.go.kr</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
